--- a/public/templates/student_masterlist_template.xlsx
+++ b/public/templates/student_masterlist_template.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,9 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +501,21 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Guardian Name</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Guardian Contact</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Guardian Relationship</t>
         </is>
       </c>
     </row>

--- a/public/templates/student_masterlist_template.xlsx
+++ b/public/templates/student_masterlist_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,25 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,90 +415,74 @@
   </sheetPr>
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Last Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>First Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Middle Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Email Address</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>College</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Year Level</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Guardian Name</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Guardian Contact</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Guardian Relationship</t>
         </is>
